--- a/artfynd/A 64303-2023 artfynd.xlsx
+++ b/artfynd/A 64303-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137151980</v>
       </c>
       <c r="B3" t="n">
-        <v>100922</v>
+        <v>100924</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137151981</v>
       </c>
       <c r="B4" t="n">
-        <v>100922</v>
+        <v>100924</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137151992</v>
       </c>
       <c r="B5" t="n">
-        <v>100922</v>
+        <v>100924</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137151932</v>
       </c>
       <c r="B6" t="n">
-        <v>111670</v>
+        <v>111672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137152050</v>
       </c>
       <c r="B7" t="n">
-        <v>106598</v>
+        <v>106600</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 64303-2023 artfynd.xlsx
+++ b/artfynd/A 64303-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137152140</v>
       </c>
       <c r="B2" t="n">
-        <v>87381</v>
+        <v>87383</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137151980</v>
       </c>
       <c r="B3" t="n">
-        <v>100924</v>
+        <v>100926</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137151981</v>
       </c>
       <c r="B4" t="n">
-        <v>100924</v>
+        <v>100926</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137151992</v>
       </c>
       <c r="B5" t="n">
-        <v>100924</v>
+        <v>100926</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137151932</v>
       </c>
       <c r="B6" t="n">
-        <v>111672</v>
+        <v>111674</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137152050</v>
       </c>
       <c r="B7" t="n">
-        <v>106600</v>
+        <v>106602</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 64303-2023 artfynd.xlsx
+++ b/artfynd/A 64303-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137152140</v>
       </c>
       <c r="B2" t="n">
-        <v>87383</v>
+        <v>87396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137151980</v>
       </c>
       <c r="B3" t="n">
-        <v>100926</v>
+        <v>100939</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137151981</v>
       </c>
       <c r="B4" t="n">
-        <v>100926</v>
+        <v>100939</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137151992</v>
       </c>
       <c r="B5" t="n">
-        <v>100926</v>
+        <v>100939</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137151932</v>
       </c>
       <c r="B6" t="n">
-        <v>111674</v>
+        <v>111687</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137152050</v>
       </c>
       <c r="B7" t="n">
-        <v>106602</v>
+        <v>106615</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 64303-2023 artfynd.xlsx
+++ b/artfynd/A 64303-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137152140</v>
       </c>
       <c r="B2" t="n">
-        <v>87396</v>
+        <v>87398</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137151980</v>
       </c>
       <c r="B3" t="n">
-        <v>100939</v>
+        <v>100941</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137151981</v>
       </c>
       <c r="B4" t="n">
-        <v>100939</v>
+        <v>100941</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137151992</v>
       </c>
       <c r="B5" t="n">
-        <v>100939</v>
+        <v>100941</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137151932</v>
       </c>
       <c r="B6" t="n">
-        <v>111687</v>
+        <v>111689</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137152050</v>
       </c>
       <c r="B7" t="n">
-        <v>106615</v>
+        <v>106617</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 64303-2023 artfynd.xlsx
+++ b/artfynd/A 64303-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137152140</v>
       </c>
       <c r="B2" t="n">
-        <v>87398</v>
+        <v>87401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137151980</v>
       </c>
       <c r="B3" t="n">
-        <v>100941</v>
+        <v>100944</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137151981</v>
       </c>
       <c r="B4" t="n">
-        <v>100941</v>
+        <v>100944</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137151992</v>
       </c>
       <c r="B5" t="n">
-        <v>100941</v>
+        <v>100944</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137151932</v>
       </c>
       <c r="B6" t="n">
-        <v>111689</v>
+        <v>111695</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137152050</v>
       </c>
       <c r="B7" t="n">
-        <v>106617</v>
+        <v>106621</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 64303-2023 artfynd.xlsx
+++ b/artfynd/A 64303-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137152140</v>
       </c>
       <c r="B2" t="n">
-        <v>87401</v>
+        <v>87411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137151980</v>
       </c>
       <c r="B3" t="n">
-        <v>100944</v>
+        <v>100954</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137151981</v>
       </c>
       <c r="B4" t="n">
-        <v>100944</v>
+        <v>100954</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137151992</v>
       </c>
       <c r="B5" t="n">
-        <v>100944</v>
+        <v>100954</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137151932</v>
       </c>
       <c r="B6" t="n">
-        <v>111695</v>
+        <v>111717</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137152050</v>
       </c>
       <c r="B7" t="n">
-        <v>106621</v>
+        <v>106641</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 64303-2023 artfynd.xlsx
+++ b/artfynd/A 64303-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137152140</v>
       </c>
       <c r="B2" t="n">
-        <v>87411</v>
+        <v>87412</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137151980</v>
       </c>
       <c r="B3" t="n">
-        <v>100954</v>
+        <v>100955</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137151981</v>
       </c>
       <c r="B4" t="n">
-        <v>100954</v>
+        <v>100955</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137151992</v>
       </c>
       <c r="B5" t="n">
-        <v>100954</v>
+        <v>100955</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137151932</v>
       </c>
       <c r="B6" t="n">
-        <v>111717</v>
+        <v>111718</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137152050</v>
       </c>
       <c r="B7" t="n">
-        <v>106641</v>
+        <v>106642</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 64303-2023 artfynd.xlsx
+++ b/artfynd/A 64303-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137152140</v>
       </c>
       <c r="B2" t="n">
-        <v>87412</v>
+        <v>87415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137151980</v>
       </c>
       <c r="B3" t="n">
-        <v>100955</v>
+        <v>100960</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137151981</v>
       </c>
       <c r="B4" t="n">
-        <v>100955</v>
+        <v>100960</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137151992</v>
       </c>
       <c r="B5" t="n">
-        <v>100955</v>
+        <v>100960</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>622342</v>
+        <v>622341</v>
       </c>
       <c r="R5" t="n">
         <v>6356585</v>
@@ -1091,7 +1091,7 @@
         <v>137151932</v>
       </c>
       <c r="B6" t="n">
-        <v>111718</v>
+        <v>111723</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137152050</v>
       </c>
       <c r="B7" t="n">
-        <v>106642</v>
+        <v>106647</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 64303-2023 artfynd.xlsx
+++ b/artfynd/A 64303-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137151980</v>
       </c>
       <c r="B3" t="n">
-        <v>100960</v>
+        <v>100963</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137151981</v>
       </c>
       <c r="B4" t="n">
-        <v>100960</v>
+        <v>100963</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137151992</v>
       </c>
       <c r="B5" t="n">
-        <v>100960</v>
+        <v>100963</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137151932</v>
       </c>
       <c r="B6" t="n">
-        <v>111723</v>
+        <v>111726</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137152050</v>
       </c>
       <c r="B7" t="n">
-        <v>106647</v>
+        <v>106650</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 64303-2023 artfynd.xlsx
+++ b/artfynd/A 64303-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137152140</v>
       </c>
       <c r="B2" t="n">
-        <v>87415</v>
+        <v>87420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137151980</v>
       </c>
       <c r="B3" t="n">
-        <v>100963</v>
+        <v>100969</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137151981</v>
       </c>
       <c r="B4" t="n">
-        <v>100963</v>
+        <v>100969</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137151992</v>
       </c>
       <c r="B5" t="n">
-        <v>100963</v>
+        <v>100969</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>622341</v>
+        <v>622342</v>
       </c>
       <c r="R5" t="n">
         <v>6356585</v>
@@ -1091,7 +1091,7 @@
         <v>137151932</v>
       </c>
       <c r="B6" t="n">
-        <v>111726</v>
+        <v>111732</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137152050</v>
       </c>
       <c r="B7" t="n">
-        <v>106650</v>
+        <v>106656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 64303-2023 artfynd.xlsx
+++ b/artfynd/A 64303-2023 artfynd.xlsx
@@ -1091,7 +1091,7 @@
         <v>137151932</v>
       </c>
       <c r="B6" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137152050</v>
       </c>
       <c r="B7" t="n">
-        <v>106656</v>
+        <v>106657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 64303-2023 artfynd.xlsx
+++ b/artfynd/A 64303-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137152140</v>
       </c>
       <c r="B2" t="n">
-        <v>87420</v>
+        <v>87431</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137151980</v>
       </c>
       <c r="B3" t="n">
-        <v>100969</v>
+        <v>100981</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137151981</v>
       </c>
       <c r="B4" t="n">
-        <v>100969</v>
+        <v>100981</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137151992</v>
       </c>
       <c r="B5" t="n">
-        <v>100969</v>
+        <v>100981</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>622342</v>
+        <v>622341</v>
       </c>
       <c r="R5" t="n">
         <v>6356585</v>
@@ -1091,7 +1091,7 @@
         <v>137151932</v>
       </c>
       <c r="B6" t="n">
-        <v>111733</v>
+        <v>111745</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137152050</v>
       </c>
       <c r="B7" t="n">
-        <v>106657</v>
+        <v>106669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 64303-2023 artfynd.xlsx
+++ b/artfynd/A 64303-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137152140</v>
       </c>
       <c r="B2" t="n">
-        <v>87431</v>
+        <v>87432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137151980</v>
       </c>
       <c r="B3" t="n">
-        <v>100981</v>
+        <v>100982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137151981</v>
       </c>
       <c r="B4" t="n">
-        <v>100981</v>
+        <v>100982</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137151992</v>
       </c>
       <c r="B5" t="n">
-        <v>100981</v>
+        <v>100982</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>622341</v>
+        <v>622342</v>
       </c>
       <c r="R5" t="n">
         <v>6356585</v>
@@ -1091,7 +1091,7 @@
         <v>137151932</v>
       </c>
       <c r="B6" t="n">
-        <v>111745</v>
+        <v>111746</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137152050</v>
       </c>
       <c r="B7" t="n">
-        <v>106669</v>
+        <v>106670</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 64303-2023 artfynd.xlsx
+++ b/artfynd/A 64303-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137152140</v>
       </c>
       <c r="B2" t="n">
-        <v>87432</v>
+        <v>87435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137151980</v>
       </c>
       <c r="B3" t="n">
-        <v>100982</v>
+        <v>100985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137151981</v>
       </c>
       <c r="B4" t="n">
-        <v>100982</v>
+        <v>100985</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137151992</v>
       </c>
       <c r="B5" t="n">
-        <v>100982</v>
+        <v>100985</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137151932</v>
       </c>
       <c r="B6" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137152050</v>
       </c>
       <c r="B7" t="n">
-        <v>106670</v>
+        <v>106673</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 64303-2023 artfynd.xlsx
+++ b/artfynd/A 64303-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137152140</v>
       </c>
       <c r="B2" t="n">
-        <v>87435</v>
+        <v>87439</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137151980</v>
       </c>
       <c r="B3" t="n">
-        <v>100985</v>
+        <v>100989</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137151981</v>
       </c>
       <c r="B4" t="n">
-        <v>100985</v>
+        <v>100989</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137151992</v>
       </c>
       <c r="B5" t="n">
-        <v>100985</v>
+        <v>100989</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137151932</v>
       </c>
       <c r="B6" t="n">
-        <v>111749</v>
+        <v>111755</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137152050</v>
       </c>
       <c r="B7" t="n">
-        <v>106673</v>
+        <v>106679</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 64303-2023 artfynd.xlsx
+++ b/artfynd/A 64303-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>137151980</v>
       </c>
       <c r="B3" t="n">
-        <v>100989</v>
+        <v>100991</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137151981</v>
       </c>
       <c r="B4" t="n">
-        <v>100989</v>
+        <v>100991</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137151992</v>
       </c>
       <c r="B5" t="n">
-        <v>100989</v>
+        <v>100991</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137151932</v>
       </c>
       <c r="B6" t="n">
-        <v>111755</v>
+        <v>111757</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137152050</v>
       </c>
       <c r="B7" t="n">
-        <v>106679</v>
+        <v>106681</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
